--- a/таблицы/V_test_case_task2.xlsx
+++ b/таблицы/V_test_case_task2.xlsx
@@ -2,60 +2,200 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="20752" windowHeight="8205" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тест-кейс Task5" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тест-кейс Task2" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Дефект 1" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="_-&quot;₽&quot;* #,##0.00_-;\-&quot;₽&quot;* #,##0.00_-;_-&quot;₽&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-* #,##0_-;\-&quot;₽&quot;* #,##0_-;_-&quot;₽&quot;* &quot;-&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
-      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <family val="0"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="Arial"/>
       <charset val="1"/>
-      <family val="0"/>
       <b val="1"/>
       <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
       <charset val="1"/>
-      <family val="0"/>
-      <sz val="11"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="36">
     <fill>
       <patternFill/>
     </fill>
@@ -80,8 +220,194 @@
         <bgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -104,181 +430,642 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="6">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
+  <cellStyles count="49">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
+    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
+    <cellStyle name="Процент" xfId="3" builtinId="5"/>
+    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
+    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
+    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
+    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
+    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
+    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
+    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
+    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
+    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
+    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
+    <cellStyle name="Итого" xfId="21" builtinId="25"/>
+    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
+    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
+    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
+    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
+    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
+    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
+    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
+    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
+    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFD9E1F2"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFC6EFCE"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFC7CE"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF999999"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00D9E1F2"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00C6EFCE"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFC7CE"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00999999"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -286,17 +1073,17 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -320,7 +1107,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -341,7 +1128,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -392,7 +1179,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -410,519 +1197,516 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:H21"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.68141592920354" defaultRowHeight="14.25"/>
   <cols>
-    <col width="6" customWidth="1" style="9" min="1" max="1"/>
-    <col width="42" customWidth="1" style="9" min="2" max="3"/>
-    <col width="7" customWidth="1" style="9" min="4" max="5"/>
-    <col width="6" customWidth="1" style="9" min="6" max="6"/>
-    <col width="42" customWidth="1" style="9" min="7" max="7"/>
-    <col width="10" customWidth="1" style="9" min="8" max="8"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="42" customWidth="1" min="2" max="3"/>
+    <col width="7" customWidth="1" min="4" max="5"/>
+    <col width="19.1858407079646" customWidth="1" min="6" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="10">
-      <c r="B1" s="11" t="inlineStr">
+    <row r="1" ht="15" customHeight="1">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Наименование:</t>
         </is>
       </c>
-      <c r="C1" s="12" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>StAlGoLM. Task2 — метод Ньютона (вариант №6)</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>№:</t>
         </is>
       </c>
-      <c r="G1" s="12" t="n">
+      <c r="G1" s="4" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="2" ht="39.55" customHeight="1" s="10">
-      <c r="B2" s="11" t="inlineStr">
+    <row r="2" ht="39.55" customHeight="1">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Описание:</t>
         </is>
       </c>
-      <c r="C2" s="13" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Тест-кейс для проверки задания Task2 (метод Ньютона) и связанной с ним авторизации</t>
         </is>
       </c>
-      <c r="F2" s="11" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>Статус:</t>
         </is>
       </c>
-      <c r="G2" s="12" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Завершён</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="10">
-      <c r="F3" s="11" t="inlineStr">
+    <row r="3" ht="15" customHeight="1">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>Дефекты №:</t>
         </is>
       </c>
-      <c r="G3" s="12" t="n">
+      <c r="G3" s="4" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="10">
-      <c r="B4" s="11" t="inlineStr">
+    <row r="4" ht="15" customHeight="1">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Тестировщик:</t>
         </is>
       </c>
-      <c r="C4" s="12" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>Голь Фёдор</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>Дата:</t>
         </is>
       </c>
-      <c r="G4" s="12" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>20.09.2026</t>
         </is>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6" ht="15" customHeight="1" s="10">
-      <c r="B6" s="11" t="inlineStr">
+    <row r="6" ht="15" customHeight="1">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Начальные условия:</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="10">
-      <c r="B7" s="14" t="inlineStr">
+    <row r="7" ht="15" customHeight="1">
+      <c r="B7" s="1" t="inlineStr">
         <is>
           <t>Параметр</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C7" s="1" t="inlineStr">
         <is>
           <t>Значение</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="26.85" customHeight="1" s="10">
-      <c r="B8" s="12" t="inlineStr">
+    <row r="8" ht="26.85" customHeight="1">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Сервер</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>StAlGoLM собран и не запущен (порт 33333 свободен)</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="10">
-      <c r="B9" s="12" t="inlineStr">
+    <row r="9" ht="15" customHeight="1">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Пользователь</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>Ещё не зарегистрирован в базе данных</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="39.55" customHeight="1" s="10">
-      <c r="B10" s="12" t="inlineStr">
+    <row r="10" ht="39.55" customHeight="1">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Соединение</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>Клиент подключается через localhost:33333, raw TCP (PuTTY или сокет-скрипт)</t>
         </is>
       </c>
     </row>
-    <row r="11"/>
-    <row r="12" ht="15" customHeight="1" s="10">
-      <c r="A12" s="15" t="inlineStr">
+    <row r="12" ht="15" customHeight="1">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Шаг</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Действие</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Ожидаемый результат</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="G12" s="15" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>Фактический результат</t>
         </is>
       </c>
-      <c r="H12" s="15" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr">
         <is>
           <t>№ дефекта</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="10">
-      <c r="A13" s="16" t="n">
+    <row r="13" ht="15" customHeight="1">
+      <c r="A13" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Запустить сервер (./StAlGoLM)</t>
         </is>
       </c>
-      <c r="C13" s="13" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>"server is started" в консоли</t>
         </is>
       </c>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="13" t="inlineStr">
+      <c r="E13" s="4" t="n"/>
+      <c r="F13" s="4" t="n"/>
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>server is started</t>
         </is>
       </c>
-      <c r="H13" s="16" t="n"/>
-    </row>
-    <row r="14" ht="26.85" customHeight="1" s="10">
-      <c r="A14" s="16" t="n">
+      <c r="H13" s="6" t="n"/>
+    </row>
+    <row r="14" ht="26.85" customHeight="1">
+      <c r="A14" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B14" s="13" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Зарегистрировать пользователя: reg newton_test pass123 newton@test.ru</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>reg+</t>
         </is>
       </c>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="13" t="inlineStr">
+      <c r="E14" s="4" t="n"/>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>reg+</t>
         </is>
       </c>
-      <c r="H14" s="16" t="n"/>
-    </row>
-    <row r="15" ht="26.85" customHeight="1" s="10">
-      <c r="A15" s="16" t="n">
+      <c r="H14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="26.85" customHeight="1">
+      <c r="A15" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B15" s="13" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>Авторизоваться тем же логином/паролем: auth newton_test pass123</t>
         </is>
       </c>
-      <c r="C15" s="13" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
         <is>
           <t>auth+ user</t>
         </is>
       </c>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="18" t="inlineStr">
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="8" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="13" t="inlineStr">
+      <c r="F15" s="4" t="n"/>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>auth- (пароль отклонён, хотя введён верно)</t>
         </is>
       </c>
-      <c r="H15" s="16" t="n">
+      <c r="H15" s="6" t="n">
         <v>1</v>
       </c>
     </row>
-    <row r="16" ht="26.85" customHeight="1" s="10">
-      <c r="A16" s="16" t="n">
+    <row r="16" ht="26.85" customHeight="1">
+      <c r="A16" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B16" s="13" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>[После исправления] Повторить: auth newton_test pass123</t>
         </is>
       </c>
-      <c r="C16" s="13" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
         <is>
           <t>auth+ user</t>
         </is>
       </c>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="13" t="inlineStr">
+      <c r="E16" s="4" t="n"/>
+      <c r="F16" s="4" t="n"/>
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>auth+ user</t>
         </is>
       </c>
-      <c r="H16" s="16" t="n"/>
-    </row>
-    <row r="17" ht="26.85" customHeight="1" s="10">
-      <c r="A17" s="16" t="n">
+      <c r="H16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="26.85" customHeight="1">
+      <c r="A17" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B17" s="13" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>Запросить задание: task2 1</t>
         </is>
       </c>
-      <c r="C17" s="13" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
         <is>
           <t>Текст задания: f(x), x0, f'(x0), формула Ньютона, 4 варианта x1</t>
         </is>
       </c>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="13" t="inlineStr">
+      <c r="E17" s="4" t="n"/>
+      <c r="F17" s="4" t="n"/>
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>Показаны f(x)=1*x^2+7*x+7, x0=1.0000, f(x0)=15.0000, f'(x0)=9.0000, 4 варианта</t>
         </is>
       </c>
-      <c r="H17" s="16" t="n"/>
-    </row>
-    <row r="18" ht="26.85" customHeight="1" s="10">
-      <c r="A18" s="16" t="n">
+      <c r="H17" s="6" t="n"/>
+    </row>
+    <row r="18" ht="26.85" customHeight="1">
+      <c r="A18" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B18" s="13" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>Ответить номером правильного варианта</t>
         </is>
       </c>
-      <c r="C18" s="13" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
         <is>
           <t>Верно! StatisticTask2[N] += 1</t>
         </is>
       </c>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="13" t="inlineStr">
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>Верно! StatisticTask2[1] += 1 (текущее значение: 0)</t>
         </is>
       </c>
-      <c r="H18" s="16" t="n"/>
-    </row>
-    <row r="19" ht="26.85" customHeight="1" s="10">
-      <c r="A19" s="16" t="n">
+      <c r="H18" s="6" t="n"/>
+    </row>
+    <row r="19" ht="26.85" customHeight="1">
+      <c r="A19" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>Запросить task2 2, ответить заведомо неверным номером</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
         <is>
           <t>Неверно! ... Правильный ответ: N</t>
         </is>
       </c>
-      <c r="D19" s="17" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="13" t="inlineStr">
+      <c r="E19" s="4" t="n"/>
+      <c r="F19" s="4" t="n"/>
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t>Неверно! StatisticTask2[2] -= 1 (текущее: 0). Правильный ответ: 1</t>
         </is>
       </c>
-      <c r="H19" s="16" t="n"/>
-    </row>
-    <row r="20"/>
-    <row r="21" ht="15" customHeight="1" s="10">
-      <c r="B21" s="11" t="inlineStr">
+      <c r="H19" s="6" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Шагов всего: 7</t>
         </is>
       </c>
-      <c r="D21" s="17" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>Pass: 6</t>
         </is>
       </c>
-      <c r="E21" s="18" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr">
         <is>
           <t>Fail: 1</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr filterMode="0">
+  <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="0"/>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B12"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.68141592920354" defaultRowHeight="14.25"/>
   <cols>
-    <col width="22" customWidth="1" style="9" min="1" max="1"/>
-    <col width="85" customWidth="1" style="9" min="2" max="2"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="85" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" s="10">
-      <c r="A1" s="14" t="inlineStr">
+    <row r="1" ht="18" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>№ дефекта</t>
         </is>
       </c>
-      <c r="B1" s="13" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="27.75" customHeight="1" s="10">
-      <c r="A2" s="14" t="inlineStr">
+    <row r="2" ht="27.75" customHeight="1">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Наименование</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Разделитель сообщения (0x01) не распознаётся, если приходит слитно с текстом команды</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="18" customHeight="1" s="10">
-      <c r="A3" s="14" t="inlineStr">
+    <row r="3" ht="18" customHeight="1">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>Обнаружен на шаге</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Тест-кейс «Task2», шаг 3 (авторизация с верным паролем)</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="18" customHeight="1" s="10">
-      <c r="A4" s="14" t="inlineStr">
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>Компонент</t>
         </is>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>mytcpserver.cpp, функция slotServerRead()</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="27.75" customHeight="1" s="10">
-      <c r="A5" s="14" t="inlineStr">
+    <row r="5" ht="27.75" customHeight="1">
+      <c r="A5" s="1" t="inlineStr">
         <is>
           <t>Критичность</t>
         </is>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Высокая — пользователь не может войти в свой аккаунт даже с верными данными</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="111.75" customHeight="1" s="10">
-      <c r="A6" s="14" t="inlineStr">
+    <row r="6" ht="111.75" customHeight="1">
+      <c r="A6" s="1" t="inlineStr">
         <is>
           <t>Описание</t>
         </is>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>Протокол сервера отделяет одну команду от другой байтом-разделителем 0x01, который клиент отправляет следом за текстом команды. Исходный код проверял условие "array == \x01", то есть ожидал, что разделитель придёт ОТДЕЛЬНЫМ, самостоятельным чтением из сокета. На практике TCP не гарантирует границ сообщений: текст команды и разделитель почти всегда приходят слитно в одном чтении (особенно на localhost). В этом случае условие не срабатывало, и байт 0x01 оставался приклеенным к последнему аргументу команды.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="69.75" customHeight="1" s="10">
-      <c r="A7" s="14" t="inlineStr">
+    <row r="7" ht="69.75" customHeight="1">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Шаги воспроизведения</t>
         </is>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>1. Зарегистрировать пользователя (reg login password email)
 2. Отправить auth login password с разделителем 0x01 сразу следом (без задержки между отправками)
@@ -930,69 +1714,68 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="18" customHeight="1" s="10">
-      <c r="A8" s="14" t="inlineStr">
+    <row r="8" ht="18" customHeight="1">
+      <c r="A8" s="1" t="inlineStr">
         <is>
           <t>Ожидаемый результат</t>
         </is>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>auth+ &lt;role&gt; — авторизация проходит успешно</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="27.75" customHeight="1" s="10">
-      <c r="A9" s="14" t="inlineStr">
+    <row r="9" ht="27.75" customHeight="1">
+      <c r="A9" s="1" t="inlineStr">
         <is>
           <t>Фактический результат</t>
         </is>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>auth- — авторизация отклонена, хотя логин и пароль верны (пароль сравнивается как «pass123\x01» против сохранённого хэша «pass123»)</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="27.75" customHeight="1" s="10">
-      <c r="A10" s="14" t="inlineStr">
+    <row r="10" ht="27.75" customHeight="1">
+      <c r="A10" s="1" t="inlineStr">
         <is>
           <t>Причина</t>
         </is>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>Для команды auth пароль — последний аргумент, поэтому именно к нему приклеивался лишний байт.</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="55.5" customHeight="1" s="10">
-      <c r="A11" s="14" t="inlineStr">
+    <row r="11" ht="55.5" customHeight="1">
+      <c r="A11" s="1" t="inlineStr">
         <is>
           <t>Исправление</t>
         </is>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>Разделитель теперь ищется внутри пришедших байт через indexOf('\x01'), а не сравнивается с ними целиком. Добавлен буфер QMap&lt;long, QByteArray&gt; mBuffers на каждого клиента, чтобы корректно собирать сообщение, даже если оно придёт по частям в нескольких чтениях подряд.</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="18" customHeight="1" s="10">
-      <c r="A12" s="14" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>Статус</t>
         </is>
       </c>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>Исправлено и проверено (см. тест-кейс Task2, шаг 4)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>